--- a/artfynd/A 52633-2023 artfynd.xlsx
+++ b/artfynd/A 52633-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>113025754</v>
       </c>
       <c r="B2" t="n">
-        <v>79092</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80303</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -714,11 +709,11 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långflon (Långflon), Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>445745</v>
+        <v>445744</v>
       </c>
       <c r="R2" t="n">
         <v>7056216</v>
@@ -784,12 +779,7 @@
         <v>113026147</v>
       </c>
       <c r="B3" t="n">
-        <v>74294</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83298</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,11 +810,11 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långflon (Långflon), Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445400</v>
+        <v>445401</v>
       </c>
       <c r="R3" t="n">
         <v>7056018</v>
@@ -890,12 +880,7 @@
         <v>114954633</v>
       </c>
       <c r="B4" t="n">
-        <v>86661</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,37 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117455528</v>
+        <v>117455549</v>
       </c>
       <c r="B5" t="n">
-        <v>97859</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445365</v>
+        <v>445345</v>
       </c>
       <c r="R5" t="n">
-        <v>7056135</v>
+        <v>7056067</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,15 +1075,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117455549</v>
+        <v>117455536</v>
       </c>
       <c r="B6" t="n">
-        <v>78482</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1111,21 +1086,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1135,10 +1110,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445345</v>
+        <v>445215</v>
       </c>
       <c r="R6" t="n">
-        <v>7056067</v>
+        <v>7055865</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1197,15 +1172,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117455547</v>
+        <v>117455538</v>
       </c>
       <c r="B7" t="n">
-        <v>90519</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1213,21 +1183,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1237,10 +1207,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445686</v>
+        <v>445370</v>
       </c>
       <c r="R7" t="n">
-        <v>7056069</v>
+        <v>7056150</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1299,66 +1269,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117455543</v>
+        <v>117455539</v>
       </c>
       <c r="B8" t="n">
-        <v>57399</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103031</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rönnöfors SÖ, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445135</v>
+        <v>445422</v>
       </c>
       <c r="R8" t="n">
-        <v>7055771</v>
+        <v>7056265</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,15 +1366,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117455538</v>
+        <v>117455542</v>
       </c>
       <c r="B9" t="n">
-        <v>79563</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1457,10 +1401,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>445370</v>
+        <v>445378</v>
       </c>
       <c r="R9" t="n">
-        <v>7056150</v>
+        <v>7056178</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1501,6 +1445,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1519,15 +1464,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117455542</v>
+        <v>117455477</v>
       </c>
       <c r="B10" t="n">
-        <v>79563</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1535,21 +1475,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1559,10 +1499,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>445378</v>
+        <v>445556</v>
       </c>
       <c r="R10" t="n">
-        <v>7056178</v>
+        <v>7056565</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,13 +1537,17 @@
           <t>2024-05-30</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1622,15 +1566,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117455536</v>
+        <v>117455478</v>
       </c>
       <c r="B11" t="n">
-        <v>79563</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1638,21 +1577,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1662,10 +1601,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445215</v>
+        <v>445592</v>
       </c>
       <c r="R11" t="n">
-        <v>7055865</v>
+        <v>7056568</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1698,6 +1637,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-05-30</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1724,15 +1668,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117455539</v>
+        <v>117455479</v>
       </c>
       <c r="B12" t="n">
-        <v>79563</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1740,21 +1679,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1764,10 +1703,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>445422</v>
+        <v>445677</v>
       </c>
       <c r="R12" t="n">
-        <v>7056265</v>
+        <v>7056472</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1800,6 +1739,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-05-30</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1826,15 +1770,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117455481</v>
+        <v>117455480</v>
       </c>
       <c r="B13" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1866,10 +1805,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>445703</v>
+        <v>445693</v>
       </c>
       <c r="R13" t="n">
-        <v>7056438</v>
+        <v>7056449</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1933,15 +1872,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117455500</v>
+        <v>117455481</v>
       </c>
       <c r="B14" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1973,10 +1907,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>445686</v>
+        <v>445703</v>
       </c>
       <c r="R14" t="n">
-        <v>7056371</v>
+        <v>7056438</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2013,7 +1947,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2040,15 +1974,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117455492</v>
+        <v>117455482</v>
       </c>
       <c r="B15" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2080,10 +2009,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>445637</v>
+        <v>445726</v>
       </c>
       <c r="R15" t="n">
-        <v>7056505</v>
+        <v>7056416</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2120,7 +2049,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2147,15 +2076,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117455493</v>
+        <v>117455483</v>
       </c>
       <c r="B16" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2187,10 +2111,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>445619</v>
+        <v>445760</v>
       </c>
       <c r="R16" t="n">
-        <v>7056496</v>
+        <v>7056302</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2227,7 +2151,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2254,15 +2178,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117455515</v>
+        <v>117455484</v>
       </c>
       <c r="B17" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2287,37 +2206,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rönnöfors SÖ, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>445405</v>
+        <v>445781</v>
       </c>
       <c r="R17" t="n">
-        <v>7056122</v>
+        <v>7056272</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2354,7 +2253,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Födosökande</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2381,15 +2280,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117455511</v>
+        <v>117455485</v>
       </c>
       <c r="B18" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2421,10 +2315,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>445532</v>
+        <v>445783</v>
       </c>
       <c r="R18" t="n">
-        <v>7056386</v>
+        <v>7056247</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2461,7 +2355,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2488,15 +2382,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117455507</v>
+        <v>117455486</v>
       </c>
       <c r="B19" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2528,10 +2417,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>445660</v>
+        <v>445775</v>
       </c>
       <c r="R19" t="n">
-        <v>7056333</v>
+        <v>7056271</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2568,7 +2457,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2595,15 +2484,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117455502</v>
+        <v>117455487</v>
       </c>
       <c r="B20" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2635,10 +2519,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>445707</v>
+        <v>445734</v>
       </c>
       <c r="R20" t="n">
-        <v>7056305</v>
+        <v>7056321</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2675,7 +2559,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2702,15 +2586,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117455498</v>
+        <v>117455488</v>
       </c>
       <c r="B21" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2742,10 +2621,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>445651</v>
+        <v>445727</v>
       </c>
       <c r="R21" t="n">
-        <v>7056439</v>
+        <v>7056371</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2782,7 +2661,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2809,15 +2688,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117455483</v>
+        <v>117455489</v>
       </c>
       <c r="B22" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2849,10 +2723,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>445760</v>
+        <v>445725</v>
       </c>
       <c r="R22" t="n">
-        <v>7056302</v>
+        <v>7056379</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2916,15 +2790,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117455516</v>
+        <v>117455490</v>
       </c>
       <c r="B23" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2956,10 +2825,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>445567</v>
+        <v>445705</v>
       </c>
       <c r="R23" t="n">
-        <v>7055955</v>
+        <v>7056427</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2996,7 +2865,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3023,15 +2892,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117455487</v>
+        <v>117455491</v>
       </c>
       <c r="B24" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3063,10 +2927,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>445734</v>
+        <v>445692</v>
       </c>
       <c r="R24" t="n">
-        <v>7056321</v>
+        <v>7056444</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3103,7 +2967,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3130,15 +2994,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117455518</v>
+        <v>117455492</v>
       </c>
       <c r="B25" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3170,10 +3029,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>445396</v>
+        <v>445637</v>
       </c>
       <c r="R25" t="n">
-        <v>7055802</v>
+        <v>7056505</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3210,7 +3069,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3237,15 +3096,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117455526</v>
+        <v>117455493</v>
       </c>
       <c r="B26" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3277,10 +3131,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>445212</v>
+        <v>445619</v>
       </c>
       <c r="R26" t="n">
-        <v>7055815</v>
+        <v>7056496</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3317,7 +3171,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3344,15 +3198,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117455522</v>
+        <v>117455494</v>
       </c>
       <c r="B27" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3384,10 +3233,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>445209</v>
+        <v>445623</v>
       </c>
       <c r="R27" t="n">
-        <v>7055691</v>
+        <v>7056511</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3424,7 +3273,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3451,15 +3300,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117455506</v>
+        <v>117455495</v>
       </c>
       <c r="B28" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3491,10 +3335,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>445664</v>
+        <v>445611</v>
       </c>
       <c r="R28" t="n">
-        <v>7056317</v>
+        <v>7056505</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3531,7 +3375,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3558,15 +3402,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117455509</v>
+        <v>117455496</v>
       </c>
       <c r="B29" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3598,10 +3437,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>445562</v>
+        <v>445607</v>
       </c>
       <c r="R29" t="n">
-        <v>7056368</v>
+        <v>7056506</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3665,15 +3504,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117455527</v>
+        <v>117455497</v>
       </c>
       <c r="B30" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3705,10 +3539,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>445515</v>
+        <v>445602</v>
       </c>
       <c r="R30" t="n">
-        <v>7056465</v>
+        <v>7056454</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3772,15 +3606,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117455488</v>
+        <v>117455498</v>
       </c>
       <c r="B31" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3812,10 +3641,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>445727</v>
+        <v>445651</v>
       </c>
       <c r="R31" t="n">
-        <v>7056371</v>
+        <v>7056439</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3852,7 +3681,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3879,15 +3708,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117455521</v>
+        <v>117455500</v>
       </c>
       <c r="B32" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3919,10 +3743,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>445221</v>
+        <v>445686</v>
       </c>
       <c r="R32" t="n">
-        <v>7055753</v>
+        <v>7056371</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3959,7 +3783,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3986,15 +3810,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117455477</v>
+        <v>117455501</v>
       </c>
       <c r="B33" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4026,10 +3845,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>445556</v>
+        <v>445697</v>
       </c>
       <c r="R33" t="n">
-        <v>7056565</v>
+        <v>7056346</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4066,7 +3885,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4093,15 +3912,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117455485</v>
+        <v>117455502</v>
       </c>
       <c r="B34" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4133,10 +3947,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>445783</v>
+        <v>445707</v>
       </c>
       <c r="R34" t="n">
-        <v>7056247</v>
+        <v>7056305</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4173,7 +3987,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4200,15 +4014,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117455508</v>
+        <v>117455503</v>
       </c>
       <c r="B35" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4240,10 +4049,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>445618</v>
+        <v>445761</v>
       </c>
       <c r="R35" t="n">
-        <v>7056367</v>
+        <v>7056234</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4280,7 +4089,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4307,15 +4116,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117455486</v>
+        <v>117455505</v>
       </c>
       <c r="B36" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4347,10 +4151,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>445775</v>
+        <v>445779</v>
       </c>
       <c r="R36" t="n">
-        <v>7056271</v>
+        <v>7056200</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4414,15 +4218,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117455482</v>
+        <v>117455506</v>
       </c>
       <c r="B37" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4454,10 +4253,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>445726</v>
+        <v>445664</v>
       </c>
       <c r="R37" t="n">
-        <v>7056416</v>
+        <v>7056317</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4494,7 +4293,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4521,15 +4320,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117455523</v>
+        <v>117455507</v>
       </c>
       <c r="B38" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4561,10 +4355,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>445188</v>
+        <v>445660</v>
       </c>
       <c r="R38" t="n">
-        <v>7055666</v>
+        <v>7056333</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4601,7 +4395,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4628,15 +4422,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117455496</v>
+        <v>117455508</v>
       </c>
       <c r="B39" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4668,10 +4457,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>445607</v>
+        <v>445618</v>
       </c>
       <c r="R39" t="n">
-        <v>7056506</v>
+        <v>7056367</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4708,7 +4497,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4735,15 +4524,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>117455489</v>
+        <v>117455509</v>
       </c>
       <c r="B40" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4775,10 +4559,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>445725</v>
+        <v>445562</v>
       </c>
       <c r="R40" t="n">
-        <v>7056379</v>
+        <v>7056368</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4815,7 +4599,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4845,12 +4629,7 @@
         <v>117455510</v>
       </c>
       <c r="B41" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4949,15 +4728,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>117455513</v>
+        <v>117455511</v>
       </c>
       <c r="B42" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4989,10 +4763,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>445552</v>
+        <v>445532</v>
       </c>
       <c r="R42" t="n">
-        <v>7056111</v>
+        <v>7056386</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5029,7 +4803,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5056,15 +4830,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>117455503</v>
+        <v>117455512</v>
       </c>
       <c r="B43" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5096,7 +4865,7 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>445761</v>
+        <v>445608</v>
       </c>
       <c r="R43" t="n">
         <v>7056234</v>
@@ -5163,15 +4932,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>117455494</v>
+        <v>117455513</v>
       </c>
       <c r="B44" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5203,10 +4967,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>445623</v>
+        <v>445552</v>
       </c>
       <c r="R44" t="n">
-        <v>7056511</v>
+        <v>7056111</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5243,7 +5007,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5270,15 +5034,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>117455501</v>
+        <v>117455515</v>
       </c>
       <c r="B45" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5303,17 +5062,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Rönnöfors SÖ, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>445697</v>
+        <v>445405</v>
       </c>
       <c r="R45" t="n">
-        <v>7056346</v>
+        <v>7056122</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5350,7 +5129,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5377,15 +5156,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>117455497</v>
+        <v>117455516</v>
       </c>
       <c r="B46" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5417,10 +5191,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>445602</v>
+        <v>445567</v>
       </c>
       <c r="R46" t="n">
-        <v>7056454</v>
+        <v>7055955</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5457,7 +5231,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5484,15 +5258,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>117455519</v>
+        <v>117455517</v>
       </c>
       <c r="B47" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5524,10 +5293,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>445256</v>
+        <v>445441</v>
       </c>
       <c r="R47" t="n">
-        <v>7055720</v>
+        <v>7055757</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5591,15 +5360,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>117455495</v>
+        <v>117455518</v>
       </c>
       <c r="B48" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5631,10 +5395,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>445611</v>
+        <v>445396</v>
       </c>
       <c r="R48" t="n">
-        <v>7056505</v>
+        <v>7055802</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5671,7 +5435,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5698,15 +5462,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>117455479</v>
+        <v>117455519</v>
       </c>
       <c r="B49" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5738,10 +5497,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>445677</v>
+        <v>445256</v>
       </c>
       <c r="R49" t="n">
-        <v>7056472</v>
+        <v>7055720</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5778,7 +5537,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5805,15 +5564,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>117455505</v>
+        <v>117455521</v>
       </c>
       <c r="B50" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5845,10 +5599,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>445779</v>
+        <v>445221</v>
       </c>
       <c r="R50" t="n">
-        <v>7056200</v>
+        <v>7055753</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5912,15 +5666,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>117455512</v>
+        <v>117455522</v>
       </c>
       <c r="B51" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5952,10 +5701,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>445608</v>
+        <v>445209</v>
       </c>
       <c r="R51" t="n">
-        <v>7056234</v>
+        <v>7055691</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5992,7 +5741,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6019,15 +5768,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>117455478</v>
+        <v>117455523</v>
       </c>
       <c r="B52" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6059,10 +5803,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>445592</v>
+        <v>445188</v>
       </c>
       <c r="R52" t="n">
-        <v>7056568</v>
+        <v>7055666</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6126,15 +5870,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>117455484</v>
+        <v>117455524</v>
       </c>
       <c r="B53" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6166,10 +5905,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>445781</v>
+        <v>445179</v>
       </c>
       <c r="R53" t="n">
-        <v>7056272</v>
+        <v>7055661</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6236,12 +5975,7 @@
         <v>117455525</v>
       </c>
       <c r="B54" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6340,15 +6074,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>117455480</v>
+        <v>117455526</v>
       </c>
       <c r="B55" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6380,10 +6109,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>445693</v>
+        <v>445212</v>
       </c>
       <c r="R55" t="n">
-        <v>7056449</v>
+        <v>7055815</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6420,7 +6149,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6447,15 +6176,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>117455491</v>
+        <v>117455527</v>
       </c>
       <c r="B56" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6487,10 +6211,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>445692</v>
+        <v>445515</v>
       </c>
       <c r="R56" t="n">
-        <v>7056444</v>
+        <v>7056465</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6527,7 +6251,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6554,15 +6278,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>117455517</v>
+        <v>117455543</v>
       </c>
       <c r="B57" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6570,16 +6289,16 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -6587,17 +6306,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Rönnöfors SÖ, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>445441</v>
+        <v>445135</v>
       </c>
       <c r="R57" t="n">
-        <v>7055757</v>
+        <v>7055771</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6630,11 +6365,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-05-30</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6661,37 +6391,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>117455490</v>
+        <v>117455528</v>
       </c>
       <c r="B58" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6701,10 +6426,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>445705</v>
+        <v>445365</v>
       </c>
       <c r="R58" t="n">
-        <v>7056427</v>
+        <v>7056135</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6737,11 +6462,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-05-30</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 52633-2023 artfynd.xlsx
+++ b/artfynd/A 52633-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY58"/>
+  <dimension ref="A1:AZ58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113025754</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113026147</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114954633</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1072,6 +1092,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117455549</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1169,6 +1194,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117455536</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1266,6 +1296,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117455538</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1363,6 +1398,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117455539</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1461,6 +1501,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117455542</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1563,6 +1608,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117455477</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1665,6 +1715,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117455478</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1767,6 +1822,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117455479</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1869,6 +1929,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117455480</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1971,6 +2036,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117455481</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2073,6 +2143,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117455482</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2175,6 +2250,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117455483</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2277,6 +2357,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117455484</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2379,6 +2464,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117455485</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2481,6 +2571,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117455486</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2583,6 +2678,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117455487</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2685,6 +2785,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117455488</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2787,6 +2892,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117455489</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2889,6 +2999,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117455490</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2991,6 +3106,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117455491</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3093,6 +3213,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117455492</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3195,6 +3320,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117455493</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3297,6 +3427,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117455494</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3399,6 +3534,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117455495</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3501,6 +3641,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117455496</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3603,6 +3748,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117455497</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3705,6 +3855,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117455498</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3807,6 +3962,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117455500</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3909,6 +4069,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117455501</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4011,6 +4176,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117455502</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4113,6 +4283,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117455503</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4215,6 +4390,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117455505</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4317,6 +4497,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117455506</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4419,6 +4604,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117455507</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4521,6 +4711,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117455508</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4623,6 +4818,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117455509</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4725,6 +4925,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117455510</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4827,6 +5032,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117455511</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4929,6 +5139,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117455512</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5031,6 +5246,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117455513</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5153,6 +5373,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117455515</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5255,6 +5480,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117455516</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5357,6 +5587,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117455517</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5459,6 +5694,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117455518</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5561,6 +5801,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117455519</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5663,6 +5908,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117455521</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5765,6 +6015,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117455522</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5867,6 +6122,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117455523</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5969,6 +6229,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117455524</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6071,6 +6336,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117455525</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6173,6 +6443,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117455526</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6275,6 +6550,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117455527</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6388,6 +6668,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117455543</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6485,8 +6770,72 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117455528</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>